--- a/data/models/lockheed-martin.xlsx
+++ b/data/models/lockheed-martin.xlsx
@@ -988,7 +988,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="12" t="n">
-        <v>602.75</v>
+        <v>590.2</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>12</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">B11*B12</f>
-        <v>139.536625</v>
+        <v>136.6313</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">B13/(B13+B14)*B10+B14/(B13+B14)*B15*(1-B16)</f>
-        <v>0.0813514074512631</v>
+        <v>0.0812377212560451</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1080,15 +1080,15 @@
       </c>
       <c r="B21" s="21" t="n">
         <f aca="false">Bear!$B$43</f>
-        <v>399.838240556129</v>
+        <v>400.640087237355</v>
       </c>
       <c r="C21" s="21" t="n">
         <f aca="false">Base!$B$43</f>
-        <v>645.798445775671</v>
+        <v>647.319114162506</v>
       </c>
       <c r="D21" s="21" t="n">
         <f aca="false">Bull!$B$43</f>
-        <v>969.770844243491</v>
+        <v>972.578448425307</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C23" s="22" t="n">
         <f aca="false">SUMPRODUCT(B21:D21,B22:D22)</f>
-        <v>665.301494087741</v>
+        <v>666.964190996919</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1119,7 +1119,7 @@
         <v>29</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>602.75</v>
+        <v>590.2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C25" s="23" t="n">
         <f aca="false">C23/C24-1</f>
-        <v>0.103776846267508</v>
+        <v>0.130064708568144</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">Summary!$B$17+B17</f>
-        <v>0.0813514074512631</v>
+        <v>0.0812377212560451</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1881,43 +1881,43 @@
       </c>
       <c r="B33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(B24-0.5)</f>
-        <v>0.961648979525043</v>
+        <v>0.961699534244814</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(C24-0.5)</f>
-        <v>0.88930293417904</v>
+        <v>0.889443195828974</v>
       </c>
       <c r="D33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(D24-0.5)</f>
-        <v>0.822399571546423</v>
+        <v>0.822615765565163</v>
       </c>
       <c r="E33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(E24-0.5)</f>
-        <v>0.760529431856766</v>
+        <v>0.760809347836618</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(F24-0.5)</f>
-        <v>0.703313859505975</v>
+        <v>0.703646693858226</v>
       </c>
       <c r="G33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(G24-0.5)</f>
-        <v>0.650402685620653</v>
+        <v>0.650778899057293</v>
       </c>
       <c r="H33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(H24-0.5)</f>
-        <v>0.601472084966022</v>
+        <v>0.601883273459329</v>
       </c>
       <c r="I33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(I24-0.5)</f>
-        <v>0.556222594081314</v>
+        <v>0.556661372080264</v>
       </c>
       <c r="J33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(J24-0.5)</f>
-        <v>0.514377278513306</v>
+        <v>0.514837173303208</v>
       </c>
       <c r="K33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(K24-0.5)</f>
-        <v>0.475680037931138</v>
+        <v>0.476155394121041</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1926,43 +1926,43 @@
       </c>
       <c r="B34" s="14" t="n">
         <f aca="false">B32*B33</f>
-        <v>6.77561090198653</v>
+        <v>6.77596710172023</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">C32*C33</f>
-        <v>6.90769499283136</v>
+        <v>6.90878448063096</v>
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">D32*D33</f>
-        <v>6.89796334451733</v>
+        <v>6.89977669470399</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">E32*E33</f>
-        <v>6.86098114858264</v>
+        <v>6.86350636086307</v>
       </c>
       <c r="F34" s="14" t="n">
         <f aca="false">F32*F33</f>
-        <v>6.71811364594083</v>
+        <v>6.72129290790684</v>
       </c>
       <c r="G34" s="14" t="n">
         <f aca="false">G32*G33</f>
-        <v>6.554548678802</v>
+        <v>6.5583400365848</v>
       </c>
       <c r="H34" s="14" t="n">
         <f aca="false">H32*H33</f>
-        <v>6.37187428158522</v>
+        <v>6.37623032977245</v>
       </c>
       <c r="I34" s="14" t="n">
         <f aca="false">I32*I33</f>
-        <v>6.17184698820069</v>
+        <v>6.17671566973237</v>
       </c>
       <c r="J34" s="14" t="n">
         <f aca="false">J32*J33</f>
-        <v>5.95636350760298</v>
+        <v>5.96168897717238</v>
       </c>
       <c r="K34" s="14" t="n">
         <f aca="false">K32*K33</f>
-        <v>5.72743053355338</v>
+        <v>5.73315406479132</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B37" s="14" t="n">
         <f aca="false">SUM(B34:K34)</f>
-        <v>64.942428023603</v>
+        <v>64.9754566238784</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B39" s="14" t="n">
         <f aca="false">B38*(1-$B$10/$B$16)/($B$18-$B$10)</f>
-        <v>208.249041949087</v>
+        <v>208.711104676637</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>87</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B40" s="14" t="n">
         <f aca="false">B39/(1+$B$18)^9.5</f>
-        <v>99.059912173465</v>
+        <v>99.3789183047418</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f aca="false">B37+B40</f>
-        <v>164.002340197068</v>
+        <v>164.35437492862</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B42" s="14" t="n">
         <f aca="false">B41+$B$19</f>
-        <v>149.502340197068</v>
+        <v>149.85437492862</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B43" s="22" t="n">
         <f aca="false">B42/$B$20</f>
-        <v>645.798445775671</v>
+        <v>647.319114162506</v>
       </c>
     </row>
   </sheetData>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">Summary!$B$17+B17</f>
-        <v>0.0913514074512631</v>
+        <v>0.0912377212560451</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2698,43 +2698,43 @@
       </c>
       <c r="B33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(B24-0.5)</f>
-        <v>0.957233069079886</v>
+        <v>0.95728293051211</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(C24-0.5)</f>
-        <v>0.877108017220048</v>
+        <v>0.877245087725019</v>
       </c>
       <c r="D33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(D24-0.5)</f>
-        <v>0.803689820924355</v>
+        <v>0.803899160226321</v>
       </c>
       <c r="E33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(E24-0.5)</f>
-        <v>0.736417083844046</v>
+        <v>0.736685641054463</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(F24-0.5)</f>
-        <v>0.674775401228346</v>
+        <v>0.67509180328418</v>
       </c>
       <c r="G33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(G24-0.5)</f>
-        <v>0.618293426499731</v>
+        <v>0.618647788776153</v>
       </c>
       <c r="H33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(H24-0.5)</f>
-        <v>0.566539267075937</v>
+        <v>0.566923023943923</v>
       </c>
       <c r="I33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(I24-0.5)</f>
-        <v>0.519117181879144</v>
+        <v>0.519522935196356</v>
       </c>
       <c r="J33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(J24-0.5)</f>
-        <v>0.475664555279667</v>
+        <v>0.476085938999955</v>
       </c>
       <c r="K33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(K24-0.5)</f>
-        <v>0.435849124335242</v>
+        <v>0.43628068360024</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2743,43 +2743,43 @@
       </c>
       <c r="B34" s="14" t="n">
         <f aca="false">B32*B33</f>
-        <v>6.08284474757187</v>
+        <v>6.08316159762742</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">C32*C33</f>
-        <v>5.99841535604479</v>
+        <v>5.99935276147917</v>
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">D32*D33</f>
-        <v>5.73662568590009</v>
+        <v>5.73811992059794</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">E32*E33</f>
-        <v>5.48531312831813</v>
+        <v>5.48731351698961</v>
       </c>
       <c r="F34" s="14" t="n">
         <f aca="false">F32*F33</f>
-        <v>5.17695078193225</v>
+        <v>5.17937825315805</v>
       </c>
       <c r="G34" s="14" t="n">
         <f aca="false">G32*G33</f>
-        <v>4.88592333228685</v>
+        <v>4.88872359966839</v>
       </c>
       <c r="H34" s="14" t="n">
         <f aca="false">H32*H33</f>
-        <v>4.6112562808787</v>
+        <v>4.6143798088858</v>
       </c>
       <c r="I34" s="14" t="n">
         <f aca="false">I32*I33</f>
-        <v>4.35202991160954</v>
+        <v>4.35543155315577</v>
       </c>
       <c r="J34" s="14" t="n">
         <f aca="false">J32*J33</f>
-        <v>4.10737621113849</v>
+        <v>4.1110148708815</v>
       </c>
       <c r="K34" s="14" t="n">
         <f aca="false">K32*K33</f>
-        <v>3.87647596236006</v>
+        <v>3.8803142839803</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B37" s="14" t="n">
         <f aca="false">SUM(B34:K34)</f>
-        <v>50.3132113980408</v>
+        <v>50.3371901664239</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B39" s="14" t="n">
         <f aca="false">B38*(1-$B$10/$B$16)/($B$18-$B$10)</f>
-        <v>130.204096147393</v>
+        <v>130.445816577043</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>87</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B40" s="14" t="n">
         <f aca="false">B39/(1+$B$18)^9.5</f>
-        <v>56.749341290703</v>
+        <v>56.9109900290239</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f aca="false">B37+B40</f>
-        <v>107.062552688744</v>
+        <v>107.248180195448</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B42" s="14" t="n">
         <f aca="false">B41+$B$19</f>
-        <v>92.5625526887438</v>
+        <v>92.7481801954478</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B43" s="22" t="n">
         <f aca="false">B42/$B$20</f>
-        <v>399.838240556129</v>
+        <v>400.640087237355</v>
       </c>
     </row>
   </sheetData>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">Summary!$B$17+B17</f>
-        <v>0.0713514074512631</v>
+        <v>0.0712377212560451</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3515,43 +3515,43 @@
       </c>
       <c r="B33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(B24-0.5)</f>
-        <v>0.966126573784586</v>
+        <v>0.966177838008275</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(C24-0.5)</f>
-        <v>0.901783081690249</v>
+        <v>0.901926639472156</v>
       </c>
       <c r="D33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(D24-0.5)</f>
-        <v>0.841724830357561</v>
+        <v>0.841948170397352</v>
       </c>
       <c r="E33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(E24-0.5)</f>
-        <v>0.785666425136845</v>
+        <v>0.785958292628225</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(F24-0.5)</f>
-        <v>0.733341478503248</v>
+        <v>0.733691763305978</v>
       </c>
       <c r="G33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(G24-0.5)</f>
-        <v>0.68450134419281</v>
+        <v>0.684900978324131</v>
       </c>
       <c r="H33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(H24-0.5)</f>
-        <v>0.638913935644359</v>
+        <v>0.639354799344698</v>
       </c>
       <c r="I33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(I24-0.5)</f>
-        <v>0.596362623132526</v>
+        <v>0.596837458818239</v>
       </c>
       <c r="J33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(J24-0.5)</f>
-        <v>0.55664520435108</v>
+        <v>0.557147537820491</v>
       </c>
       <c r="K33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(K24-0.5)</f>
-        <v>0.519572943554846</v>
+        <v>0.520097011863273</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3560,43 +3560,43 @@
       </c>
       <c r="B34" s="14" t="n">
         <f aca="false">B32*B33</f>
-        <v>7.01653385330008</v>
+        <v>7.01690616182645</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">C32*C33</f>
-        <v>7.43636120157916</v>
+        <v>7.43754502010628</v>
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">D32*D33</f>
-        <v>7.75010752624214</v>
+        <v>7.75216391006362</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">E32*E33</f>
-        <v>8.01963084126281</v>
+        <v>8.02261005669132</v>
       </c>
       <c r="F34" s="14" t="n">
         <f aca="false">F32*F33</f>
-        <v>8.0613344941245</v>
+        <v>8.06518503721498</v>
       </c>
       <c r="G34" s="14" t="n">
         <f aca="false">G32*G33</f>
-        <v>8.05519535206547</v>
+        <v>8.05989823690924</v>
       </c>
       <c r="H34" s="14" t="n">
         <f aca="false">H32*H33</f>
-        <v>8.00105570908677</v>
+        <v>8.006576601385</v>
       </c>
       <c r="I34" s="14" t="n">
         <f aca="false">I32*I33</f>
-        <v>7.89961472112351</v>
+        <v>7.90590455020983</v>
       </c>
       <c r="J34" s="14" t="n">
         <f aca="false">J32*J33</f>
-        <v>7.75241559762615</v>
+        <v>7.75941161195094</v>
       </c>
       <c r="K34" s="14" t="n">
         <f aca="false">K32*K33</f>
-        <v>7.56180762475298</v>
+        <v>7.56943485742494</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B37" s="14" t="n">
         <f aca="false">SUM(B34:K34)</f>
-        <v>77.5540569211636</v>
+        <v>77.5956360437826</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="B39" s="14" t="n">
         <f aca="false">B38*(1-$B$10/$B$16)/($B$18-$B$10)</f>
-        <v>310.731910743082</v>
+        <v>311.588551885929</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>87</v>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B40" s="14" t="n">
         <f aca="false">B39/(1+$B$18)^9.5</f>
-        <v>161.447893521205</v>
+        <v>162.056274766676</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f aca="false">B37+B40</f>
-        <v>239.001950442368</v>
+        <v>239.651910810459</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B42" s="14" t="n">
         <f aca="false">B41+$B$19</f>
-        <v>224.501950442368</v>
+        <v>225.151910810459</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B43" s="22" t="n">
         <f aca="false">B42/$B$20</f>
-        <v>969.770844243491</v>
+        <v>972.578448425307</v>
       </c>
     </row>
   </sheetData>
